--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\SeketalaFolder\seketalaNew\cache\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867BA7FC-8662-4D7A-8D54-85A5E72CFF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D70C31-8D9E-4D81-BA41-2BCEA9769975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1926,10 +1926,10 @@
     <t>قوطي زيرو کوکا با ليوان</t>
   </si>
   <si>
-    <t>لیموناد ۲۵۰ سیسی لاکی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لیموناد قوطی خوشگوار </t>
+    <t>ليموناد 250 سيسي لاکي</t>
+  </si>
+  <si>
+    <t>ليموناد قوطي خوشگوار</t>
   </si>
 </sst>
 </file>
@@ -1993,7 +1993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2004,6 +2004,7 @@
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5664,7 +5665,7 @@
       <c r="A344">
         <v>1100076</v>
       </c>
-      <c r="B344" s="9" t="s">
+      <c r="B344" s="10" t="s">
         <v>634</v>
       </c>
       <c r="Z344" s="7"/>

--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D70C31-8D9E-4D81-BA41-2BCEA9769975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF835C41-1BA3-478B-96A3-FDE083A87B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="21540" windowHeight="11355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="639">
   <si>
     <t>كد</t>
   </si>
@@ -1930,6 +1930,18 @@
   </si>
   <si>
     <t>ليموناد قوطي خوشگوار</t>
+  </si>
+  <si>
+    <t>هافنبرگ بلوبري با ليوان</t>
+  </si>
+  <si>
+    <t>هافنبرگ ليموناد با ليوان</t>
+  </si>
+  <si>
+    <t>هافنبرگ سيب کيوي با ليوان</t>
+  </si>
+  <si>
+    <t>اب گازدار ليمويي (بدون قند)</t>
   </si>
 </sst>
 </file>
@@ -5671,19 +5683,43 @@
       <c r="Z344" s="7"/>
       <c r="AB344" s="7"/>
     </row>
-    <row r="345" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>1100091</v>
+      </c>
+      <c r="B345" s="9" t="s">
+        <v>636</v>
+      </c>
       <c r="Z345" s="7"/>
       <c r="AB345" s="7"/>
     </row>
     <row r="346" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>1100090</v>
+      </c>
+      <c r="B346" t="s">
+        <v>635</v>
+      </c>
       <c r="Z346" s="7"/>
       <c r="AB346" s="7"/>
     </row>
     <row r="347" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>1100092</v>
+      </c>
+      <c r="B347" t="s">
+        <v>637</v>
+      </c>
       <c r="Z347" s="7"/>
       <c r="AB347" s="7"/>
     </row>
     <row r="348" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>1100089</v>
+      </c>
+      <c r="B348" t="s">
+        <v>638</v>
+      </c>
       <c r="Z348" s="7"/>
       <c r="AB348" s="7"/>
     </row>
